--- a/new/260802.xlsx
+++ b/new/260802.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51CD4E1-9EB6-42E1-90AF-8F57A4685F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD4BA07-D805-4FA9-A569-B033645A7C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5230" yWindow="3340" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6660" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>每周采访-160731-Generalbundesanwalt</t>
   </si>
@@ -120,89 +121,6 @@
 Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
 Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
 Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Und die Zeit, in der sie immer vertröstet wurden, dass das nun mal so ist in der Globalisierung, dass man das nicht alles machen kann und wir kein Geld haben, da sehen die Menschen jeden Tag, dass wir für alles mögliche Geld haben und erwarten – zu Recht –, dass wir diese ganz normalen Bedürfnisse auch erfüllen in unserem Land.
-Geers: Ist das jetzt gerade der Einblick gewesen in das, womit Ihre Partei im nächsten Jahr punkten will in der Bundestagswahl?
-Ich frage das auch vor dem Hintergrund, dass Ihr Hauptgegner, sprich die CDU/CSU, einen eher personalisierten, auf Angela Merkel zugeschnittenen Wahlkampf führen dürfte – den Sie dann mit SPD mit Sachthemen kontern werden?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir müssen die Ausgaben für Forschung und Entwicklung erhöhen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Also jedenfalls ist das, glaube ich, was Vernünftiges, dass wir sagen, was wir machen wollen im Land.
-Ich will vielleicht noch etwas hinzufügen, was genauso wichtig ist.
-Wenn man das alles schaffen will, auch wieder mehr Sicherheit – soziale wie innere – zu schaffen, muss man ja sagen: Wo kommt das Geld eigentlich her dafür?
-Und ich glaube, was das Wichtigste ist, dass wir alles dafür tun, dass unser Land wirtschaftlich erfolgreich bleibt.
-Meine Sorge – und das muss auch ein Thema im Wahlkampf sein – ist, dass wir zu viel, sagen wir mal, uns ausruhen auf den Anstrengungen der Vergangenheit und dass wir ein bisschen zu wenig dafür tun, was morgen kommt.
-Ich glaube, wir müssen unsere Ausgaben für Forschung und Entwicklung erhöhen.
-Wir werden dafür sorgen müssen, dass junge Unternehmen mehr Chancen haben.
-Wir müssen dafür sorgen, dass die berufliche Bildung wieder an Stellenwert gewinnt – wir haben einen Fachkräftemangel bei uns.
-In der Energiepolitik haben wir, Gott sei Dank, viel geschafft, sie ist endlich wieder planbar und berechenbar geworden.
-Aber es wird auch darum gehen müssen, Investitionen in die Digitalisierung zu schaffen, die Infrastruktur zu verbessern.
-Nur wenn wir gute wirtschaftliche Rahmenbedingungen haben, dann bleibt es so wie heute, dass wir eine hohe Beschäftigtenzahl haben, dass wir endlich wieder steigende Löhne haben, auch besser Renten haben.
-Wir haben jetzt eine Rentenerhöhung gehabt, die hatten wir in den letzten 20 Jahren nicht so hoch, mit knapp sechs Prozent.
-Das, glaube ich, gehört auch dazu, dass wir in den nächsten zwölf Monaten auch darüber diskutieren müssen in Deutschland: Was ist notwendig, damit das Land erfolgreich bleibt.
-Das sind die beiden Dinge, mehr Sicherheit zu schaffen, aber auch den Erfolg der deutschen Wirtschaft, die Schaffung von Arbeitsplätzen zum Thema zu machen.
-Ich fände es jedenfalls gut, wenn es in einem Bundestagswahlkampf um die Zukunft unseres Landes ginge und nicht nur um die Frage, wer irgendwie die besten Personen aufstellt.
-Geers: Die SPD muss natürlich auch die Frage beantworten: Wie wird das bezahlt?
-Also, wenn ich jetzt überlege oder wenn ich jetzt zusammenzähle: Mehr innere Sicherheit, mehr äußere Sicherheit, Bekämpfung des Terrorismus, Bekämpfung vielleicht auch von Fluchtursachen in Ländern wie Syrien oder in Afrika, wenn ich an weitere Stichworte, die auch immer in der Debatte fallen, wie mehr Geld für die Bundeswehr oder – wie Sie es gerade gesagt haben, Herr Gabriel – mehr Geld für soziale Sicherheit, für den sozialen Zusammenhalt im Land, mehr Geld für Bildung, vielleicht auch mehr Geld für Wachstum in Europa nach einem möglichen Brexit, da kommt Vieles zusammen.
-Und dann muss natürlich auch die SPD Antwort geben darauf, dass es das alles nicht zum Nulltarif gibt.
-Also, woher kommt das Geld?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Formen legaler Steuervermeidung bekämpfen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Erstens haben wir das große Glück, dass wir in einer Phase leben, wo es uns wirtschaftlich gut geht und wir Überschüsse produzieren.
-Wir wären nicht klug beraten, wenn wir die nicht investieren würden in Bildung und in Infrastruktur - das ist die Zukunft unseres Landes.
-Zweitens wird es auch darum gehen - Sie haben das Stichwort völlig zurecht genannt -, was machen wir eigentlich in Europa.
-In Europa ist es heute so, dass jeder Bäckermeister in Deutschland höhere Steuersätze zahlt als große Konzerne wie Amazon, Google und manche anderen, Starbucks, weil wir in Europa Steueroasen haben und dann gigantische Gewinne zum Beispiel in Deutschland gemacht werden, aber nur ein Prozent Steuern gezahlt werden.
-Unser Land verliert nach Berechnungen der Europäischen Kommission in jedem Jahr 150 Milliarden Euro durch diese Form legaler Steuervermeidung - das ist die Hälfte des Bundeshaushaltes!
-Ich glaube nun auch nicht, dass wir das alles kriegen werden, aber stellen Sie sich vor, wir würden es schaffen, wenigstens zehn Prozent davon zu bekommen, indem wir in Europa diese Briefkastenfirmen bekämpfen, dass wir eine gemeinsame Grundlage der Besteuerung haben.
-Ich will ja gar nicht gleiche Steuersätze - das ist eine Illusion, das wird man nicht hinkriegen -, aber dass wir uns wenigstens darauf verständigen, was besteuern wir.
-Das muss Europa schaffen.
-Wenn nicht, werden die Menschen immer weniger bereit sein, sagen wir mal, in Europa etwas zu erkennen, was ihren Lebensinteressen entspricht.
-Und es kann nicht sein, dass der Stärkste sich davor drückt, zum Gemeinwohl beizutragen.
-Das ist auch ein großes europäisches Thema.
-Geers: Das heißt aber auch, aus Ihrer Sicht wackelt dann zum Beispiel das Thema Haushaltsausgleich – dann wackelt die schwarze Null nicht unbedingt?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es ist kein Ziel per se, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Also, ich weiß nicht genau, warum man Spaß daran haben soll, Schulden zu machen, sondern das Schönste ist natürlich, wenn man keine macht.
-Und deswegen, es ist ja kein Ziel per se, Schulden zu machen.
-Ich glaube, dass die Frage, ob man sich verschuldet oder nicht, mit zwei zentralen Fragen zu tun hat.
-Erstens, sind es Daueraufgaben, für die man sich verschuldet, dann darf man das eigentlich nicht machen.
-Oder sind es Investitionen, die man tätigt, damit die Bedingungen gut werden in der Infrastruktur, in der Digitalisierung, dann darf man das natürlich, wenn man eine zweite Bedingung einhält und gleich klärt, wie man eigentlich das wieder abbezahlt.
-Und der Fehler der Politik der Vergangenheit ist in der Regel gewesen, dass sich gerade um die zweite Frage keiner Gedanken gemacht hat.
-Ich persönlich bin froh darüber, dass wir in einer Situation leben, in der wir das nicht müssen, in der wir ausgeglichene Haushalte haben.
-Und das ist der Grund, warum ich als Wirtschaftsminister sage: Das klappt alles nur, weil wir eine gut laufende Wirtschaft haben.
-Und das bedeutet: Wer das in Zukunft auch haben will, der muss die Bedingungen für erfolgreiche Wirtschaft in Deutschland gut halten.
-Und da gibt es eine Reihe von Dingen, wo wir in den letzten Jahren, glaube ich, nicht genug gemacht haben.
-Geers: Als da wären?
-Gabriel: Zum Beispiel die Entlastung von mittelständischen Unternehmen dort, wo sie junge Unternehmen haben, wo die Unternehmen investieren wollen.
-Wir haben Regeln,die zum Teil 15,20 Jahre alt sind bei der Frage, was können sie an kurzlebigen Wirtschaftsgütern von der Steuer absetzen, welche Vorschriften müssen sie einhalten, wenn sie ein junges Unternehmen gründen.
-Wir haben jetzt, Gott sei Dank, zwei Bürokratieentlastungsgesetze mit insgesamt mit mehr als zwei Milliarden Euro Entlastung gemacht.
-Aber ich sage Ihnen: Da ist noch mehr drin!
-Dann die Frage Fachkräfte, die Digitalisierung.
-Wir werden in Deutschland auf Sicht keine Chance haben, wirtschaftliche Erfolge zu haben, wenn wir nicht wesentlich besser werden bei der digitalen Infrastruktur.
-Wir haben jetzt ein Ziel von 50 Megabit pro Sekunde im Jahr 2018.
-Das ist in Ordnung, aber jeder weiß: Das ist viel zu wenig.
-Eigentlich muss Deutschland, muss sich Europa das Ziel setzen, im Jahr 2025 die beste digitale Infrastruktur der Welt zu haben – ohne das werden wir das nicht schaffen.
-Das sind Dinge, die als Voraussetzung geschaffen werden müssen, damit die Wirtschaft gut läuft.
-Geers: Würden Sie soweit gehen, Herr Gabriel, dass Sie sagen, mit Blick auch auf die aktuell ja eher günstige Lage, was die Finanzierungsmöglichkeiten des Staates betrifft – er zahlt ja so gut wie keine Zinsen derzeit, der Staat, Deutschland –, dass man diese Zeiten nutzen sollte möglicherweise, um auch für solche Projekt, die man ja definieren könnte als sinnvoll, zukunftsgewandt und, und, und, dass man sagt, für solche Projekte machen wir auch Schulden und haben dann eben jetzt die Möglichkeit, jetzt für vergleichsweise preiswertes Geld Zukunftsinvestitionen zu tätigen?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Für die Digitalisierung wäre ich dafür, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Alle auf der Welt sagen uns das. Alle. Es gibt nur einen, der anderer Meinung ist, das ist der Bundesfinanzminister.
-Weil alle Ökonomen sagen: 'Ihr seid ja verrückt, dass ihr eure Schulen und eure Infrastruktur verkommen lasst in einer Zeit, wo euch die Investitionen zur Sanierung von Infrastruktur und Schulen nichts kostet und in paar Jahren müsst ihr es dann doch machen und wenn ihr Pech habt, sind die Zinsen dann höher.
-' Es spricht viel dafür, für Investitionen in die Infrastruktur im Zweifel auch bereit zu sein, sich zu verschulden.
-Aber ich sage noch mal: Das kann kein Ziel an sich sein.
-Zurzeit haben wir mit Hilfe auch von Wolfgang Schäuble und der Bundesregierung insgesamt ja zum Beispiel die kommunale Investitionsmöglichkeit deutlich erhöht und mussten dafür überhaupt keine Schulden machen.
-Zweitens, wenn man das macht – zum Beispiel für die Digitalisierung wäre ich dafür, es zu tun –, dann muss man auch eine Vorstellung darüber haben, wie man das zurückzahlt.
-Ein Thema dabei ist – muss man auch offen sagen –, dass ich zum Beispiel glaube, dass es nicht in Ordnung ist, dass wir die Einkommen durch Arbeit stärker besteuern als die Einkommen die man hat, wenn man Aktien besitzt.
-Es kann ja nicht sein, dass einer, der arbeiten geht, höhere Steuern zahlt auf den gleichen Betrag, als jemand, der auf dem Sofa liegt und das über die Aktien bekommt.
-Das haben wir mal eingeführt, weil wir gehofft haben, dass die Steuerflucht nachlässt.
-Heute haben wir Datenaustausch, es gibt kein Bankgeheimnis mehr, wir können die Steuerhinterziehung anders bekämpfen.
-Geers: Also, Abgeltungssteuer abschaffen?
-Gabriel: Die Abgeltungssteuer ist der Fachbegriff dafür.
-Und das Geld, das wir dort bekommen, sollten wir ausschließlich in den Bildungsbereich stecken.
-Ein großes Schulsanierungsprogramm, Sanierung der Sportstätten, Einstellung von Sozialpädagogen in den Ganztagsschulen.
-Das wäre ein großes Programm, was auch mal zeigen würde: Bildung ist uns was wert!
-Geers: Sagt Sigmar Gabriel, der Vizekanzler, der SPD-Chef und der mögliche SPD-Kanzlerkandidat, der dabei bleibt, dass diese Entscheidung erst Anfang nächsten Jahres getroffen wird?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Erst mal sagen, was man will und dann eine Person bestimmen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Ich habe schon darauf gewartet, dass die Frage kommt.
-Geers: Ich stelle sie am Schluss.
-Gabriel: Ja, ist ja auch in Ordnung.
-Ich meine, ich will es einfach nur erklären.
-Wenn wir jetzt anfangen, Personal bei uns zu debattieren, können Sie als Journalisten überhaupt nicht anders, als nur darüber zu reden.
-In dem Interview hier war es deshalb gut, weil wir fast nur über Sachfragen geredet haben, sonst hätten wir ausschließlich über Personen geredet – ist meine Vermutung.
-Und ich glaube, dass es klug ist, erst mal zu sagen, was man will und dann am Ende auch eine Person – natürlich brauchen wir die – zu bestimmen und es nicht umgekehrt zu machen.
-Und dann bin ich ein bisschen lästerlich und sage: Solange die Kanzlerin noch nicht einmal gesagt hat, ob sie noch mal kandidiert, müssen wir noch keinen Kandidaten nennen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -630,6 +548,88 @@
 Scholz: Er ist nicht der Erste, der das tut.
 Minister, die dieses Amt vor ihm hatten.
 Das könnte die Zeit sein, eine vorläufige Bilanz der Großen Koalition zu ziehen, mit der sich Ihre Partei, die SPD, am Anfang ja schwergetan hat.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>In der Energiepolitik haben wir, Gott sei Dank, viel geschafft, sie ist endlich wieder planbar und berechenbar geworden.
+Aber es wird auch darum gehen müssen, Investitionen in die Digitalisierung zu schaffen, die Infrastruktur zu verbessern.
+Nur wenn wir gute wirtschaftliche Rahmenbedingungen haben, dann bleibt es so wie heute, dass wir eine hohe Beschäftigtenzahl haben, dass wir endlich wieder steigende Löhne haben, auch besser Renten haben.
+Wir haben jetzt eine Rentenerhöhung gehabt, die hatten wir in den letzten 20 Jahren nicht so hoch, mit knapp sechs Prozent.
+Das, glaube ich, gehört auch dazu, dass wir in den nächsten zwölf Monaten auch darüber diskutieren müssen in Deutschland: Was ist notwendig, damit das Land erfolgreich bleibt.
+Das sind die beiden Dinge, mehr Sicherheit zu schaffen, aber auch den Erfolg der deutschen Wirtschaft, die Schaffung von Arbeitsplätzen zum Thema zu machen.
+Ich fände es jedenfalls gut, wenn es in einem Bundestagswahlkampf um die Zukunft unseres Landes ginge und nicht nur um die Frage, wer irgendwie die besten Personen aufstellt.
+Geers: Die SPD muss natürlich auch die Frage beantworten: Wie wird das bezahlt?
+Also, wenn ich jetzt überlege oder wenn ich jetzt zusammenzähle: Mehr innere Sicherheit, mehr äußere Sicherheit, Bekämpfung des Terrorismus, Bekämpfung vielleicht auch von Fluchtursachen in Ländern wie Syrien oder in Afrika, wenn ich an weitere Stichworte, die auch immer in der Debatte fallen, wie mehr Geld für die Bundeswehr oder – wie Sie es gerade gesagt haben, Herr Gabriel – mehr Geld für soziale Sicherheit, für den sozialen Zusammenhalt im Land, mehr Geld für Bildung, vielleicht auch mehr Geld für Wachstum in Europa nach einem möglichen Brexit, da kommt Vieles zusammen.
+Und dann muss natürlich auch die SPD Antwort geben darauf, dass es das alles nicht zum Nulltarif gibt.
+Also, woher kommt das Geld?
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Formen legaler Steuervermeidung bekämpfen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Erstens haben wir das große Glück, dass wir in einer Phase leben, wo es uns wirtschaftlich gut geht und wir Überschüsse produzieren.
+Wir wären nicht klug beraten, wenn wir die nicht investieren würden in Bildung und in Infrastruktur - das ist die Zukunft unseres Landes.
+Zweitens wird es auch darum gehen - Sie haben das Stichwort völlig zurecht genannt -, was machen wir eigentlich in Europa.
+In Europa ist es heute so, dass jeder Bäckermeister in Deutschland höhere Steuersätze zahlt als große Konzerne wie Amazon, Google und manche anderen, Starbucks, weil wir in Europa Steueroasen haben und dann gigantische Gewinne zum Beispiel in Deutschland gemacht werden, aber nur ein Prozent Steuern gezahlt werden.
+Unser Land verliert nach Berechnungen der Europäischen Kommission in jedem Jahr 150 Milliarden Euro durch diese Form legaler Steuervermeidung - das ist die Hälfte des Bundeshaushaltes!
+Ich glaube nun auch nicht, dass wir das alles kriegen werden, aber stellen Sie sich vor, wir würden es schaffen, wenigstens zehn Prozent davon zu bekommen, indem wir in Europa diese Briefkastenfirmen bekämpfen, dass wir eine gemeinsame Grundlage der Besteuerung haben.
+Ich will ja gar nicht gleiche Steuersätze - das ist eine Illusion, das wird man nicht hinkriegen -, aber dass wir uns wenigstens darauf verständigen, was besteuern wir.
+Das muss Europa schaffen.
+Wenn nicht, werden die Menschen immer weniger bereit sein, sagen wir mal, in Europa etwas zu erkennen, was ihren Lebensinteressen entspricht.
+Und es kann nicht sein, dass der Stärkste sich davor drückt, zum Gemeinwohl beizutragen.
+Das ist auch ein großes europäisches Thema.
+Geers: Das heißt aber auch, aus Ihrer Sicht wackelt dann zum Beispiel das Thema Haushaltsausgleich – dann wackelt die schwarze Null nicht unbedingt?
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es ist kein Ziel per se, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Also, ich weiß nicht genau, warum man Spaß daran haben soll, Schulden zu machen, sondern das Schönste ist natürlich, wenn man keine macht.
+Und deswegen, es ist ja kein Ziel per se, Schulden zu machen.
+Ich glaube, dass die Frage, ob man sich verschuldet oder nicht, mit zwei zentralen Fragen zu tun hat.
+Erstens, sind es Daueraufgaben, für die man sich verschuldet, dann darf man das eigentlich nicht machen.
+Oder sind es Investitionen, die man tätigt, damit die Bedingungen gut werden in der Infrastruktur, in der Digitalisierung, dann darf man das natürlich, wenn man eine zweite Bedingung einhält und gleich klärt, wie man eigentlich das wieder abbezahlt.
+Und der Fehler der Politik der Vergangenheit ist in der Regel gewesen, dass sich gerade um die zweite Frage keiner Gedanken gemacht hat.
+Ich persönlich bin froh darüber, dass wir in einer Situation leben, in der wir das nicht müssen, in der wir ausgeglichene Haushalte haben.
+Und das ist der Grund, warum ich als Wirtschaftsminister sage: Das klappt alles nur, weil wir eine gut laufende Wirtschaft haben.
+Und das bedeutet: Wer das in Zukunft auch haben will, der muss die Bedingungen für erfolgreiche Wirtschaft in Deutschland gut halten.
+Und da gibt es eine Reihe von Dingen, wo wir in den letzten Jahren, glaube ich, nicht genug gemacht haben.
+Geers: Als da wären?
+Gabriel: Zum Beispiel die Entlastung von mittelständischen Unternehmen dort, wo sie junge Unternehmen haben, wo die Unternehmen investieren wollen.
+Wir haben Regeln,die zum Teil 15,20 Jahre alt sind bei der Frage, was können sie an kurzlebigen Wirtschaftsgütern von der Steuer absetzen, welche Vorschriften müssen sie einhalten, wenn sie ein junges Unternehmen gründen.
+Wir haben jetzt, Gott sei Dank, zwei Bürokratieentlastungsgesetze mit insgesamt mit mehr als zwei Milliarden Euro Entlastung gemacht.
+Aber ich sage Ihnen: Da ist noch mehr drin!
+Dann die Frage Fachkräfte, die Digitalisierung.
+Wir werden in Deutschland auf Sicht keine Chance haben, wirtschaftliche Erfolge zu haben, wenn wir nicht wesentlich besser werden bei der digitalen Infrastruktur.
+Wir haben jetzt ein Ziel von 50 Megabit pro Sekunde im Jahr 2018.
+Das ist in Ordnung, aber jeder weiß: Das ist viel zu wenig.
+Eigentlich muss Deutschland, muss sich Europa das Ziel setzen, im Jahr 2025 die beste digitale Infrastruktur der Welt zu haben – ohne das werden wir das nicht schaffen.
+Das sind Dinge, die als Voraussetzung geschaffen werden müssen, damit die Wirtschaft gut läuft.
+Geers: Würden Sie soweit gehen, Herr Gabriel, dass Sie sagen, mit Blick auch auf die aktuell ja eher günstige Lage, was die Finanzierungsmöglichkeiten des Staates betrifft – er zahlt ja so gut wie keine Zinsen derzeit, der Staat, Deutschland –, dass man diese Zeiten nutzen sollte möglicherweise, um auch für solche Projekt, die man ja definieren könnte als sinnvoll, zukunftsgewandt und, und, und, dass man sagt, für solche Projekte machen wir auch Schulden und haben dann eben jetzt die Möglichkeit, jetzt für vergleichsweise preiswertes Geld Zukunftsinvestitionen zu tätigen?
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Für die Digitalisierung wäre ich dafür, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Alle auf der Welt sagen uns das. Alle. Es gibt nur einen, der anderer Meinung ist, das ist der Bundesfinanzminister.
+Weil alle Ökonomen sagen: 'Ihr seid ja verrückt, dass ihr eure Schulen und eure Infrastruktur verkommen lasst in einer Zeit, wo euch die Investitionen zur Sanierung von Infrastruktur und Schulen nichts kostet und in paar Jahren müsst ihr es dann doch machen und wenn ihr Pech habt, sind die Zinsen dann höher.
+' Es spricht viel dafür, für Investitionen in die Infrastruktur im Zweifel auch bereit zu sein, sich zu verschulden.
+Aber ich sage noch mal: Das kann kein Ziel an sich sein.
+Zurzeit haben wir mit Hilfe auch von Wolfgang Schäuble und der Bundesregierung insgesamt ja zum Beispiel die kommunale Investitionsmöglichkeit deutlich erhöht und mussten dafür überhaupt keine Schulden machen.
+Zweitens, wenn man das macht – zum Beispiel für die Digitalisierung wäre ich dafür, es zu tun –, dann muss man auch eine Vorstellung darüber haben, wie man das zurückzahlt.
+Ein Thema dabei ist – muss man auch offen sagen –, dass ich zum Beispiel glaube, dass es nicht in Ordnung ist, dass wir die Einkommen durch Arbeit stärker besteuern als die Einkommen die man hat, wenn man Aktien besitzt.
+Es kann ja nicht sein, dass einer, der arbeiten geht, höhere Steuern zahlt auf den gleichen Betrag, als jemand, der auf dem Sofa liegt und das über die Aktien bekommt.
+Das haben wir mal eingeführt, weil wir gehofft haben, dass die Steuerflucht nachlässt.
+Heute haben wir Datenaustausch, es gibt kein Bankgeheimnis mehr, wir können die Steuerhinterziehung anders bekämpfen.
+Geers: Also, Abgeltungssteuer abschaffen?
+Gabriel: Die Abgeltungssteuer ist der Fachbegriff dafür.
+Und das Geld, das wir dort bekommen, sollten wir ausschließlich in den Bildungsbereich stecken.
+Ein großes Schulsanierungsprogramm, Sanierung der Sportstätten, Einstellung von Sozialpädagogen in den Ganztagsschulen.
+Das wäre ein großes Programm, was auch mal zeigen würde: Bildung ist uns was wert!
+Geers: Sagt Sigmar Gabriel, der Vizekanzler, der SPD-Chef und der mögliche SPD-Kanzlerkandidat, der dabei bleibt, dass diese Entscheidung erst Anfang nächsten Jahres getroffen wird?
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Erst mal sagen, was man will und dann eine Person bestimmen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Ich habe schon darauf gewartet, dass die Frage kommt.
+Geers: Ich stelle sie am Schluss.
+Gabriel: Ja, ist ja auch in Ordnung.
+Ich meine, ich will es einfach nur erklären.
+Wenn wir jetzt anfangen, Personal bei uns zu debattieren, können Sie als Journalisten überhaupt nicht anders, als nur darüber zu reden.
+In dem Interview hier war es deshalb gut, weil wir fast nur über Sachfragen geredet haben, sonst hätten wir ausschließlich über Personen geredet – ist meine Vermutung.
+Und ich glaube, dass es klug ist, erst mal zu sagen, was man will und dann am Ende auch eine Person – natürlich brauchen wir die – zu bestimmen und es nicht umgekehrt zu machen.
+Und dann bin ich ein bisschen lästerlich und sage: Solange die Kanzlerin noch nicht einmal gesagt hat, ob sie noch mal kandidiert, müssen wir noch keinen Kandidaten nennen"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Und die Zeit, in der sie immer vertröstet wurden, dass das nun mal so ist in der Globalisierung, dass man das nicht alles machen kann und wir kein Geld haben.
+Geers: Ist das jetzt gerade der Einblick gewesen in das, auf Angela Merkel zugeschnittenen Wahlkampf führen dürfte – den Sie dann mit SPD mit Sachthemen kontern werden?
+Wenn man das alles schaffen will, auch wieder mehr Sicherheit – soziale wie innere – zu schaffen, muss man ja sagen: Wo kommt das Geld eigentlich her dafür?
+zu viel, sagen wir mal, uns ausruhen auf den.
+Ich glaube, wir müssen unsere Ausgaben für Forschung und Entwicklung erhöhen.
+Wir werden dafür sorgen müssen, dass junge Unternehmen mehr Chancen haben.
+Wir müssen dafür sorgen, dass die berufliche Bildung wieder an Stellenwert gewinnt – wir haben einen Fachkräftemangel bei uns.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -966,7 +966,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -976,6 +976,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ABC75E4-C580-4C0E-A208-D1C6CCABB61F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.08203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="378" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -1009,16 +1028,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/new/260802.xlsx
+++ b/new/260802.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD4BA07-D805-4FA9-A569-B033645A7C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752C6084-23C9-4920-BCEB-E13D99F34A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10320" yWindow="3760" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>每周采访-160731-Generalbundesanwalt</t>
   </si>
@@ -121,111 +122,6 @@
 Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
 Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
 Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACEA oder aber auch andere Verbände in den USA. Es ist auch ein klassisches Feld, wo eben es noch keine neuen Rahmenbedingungen gibt, wo wir sehr, sehr gut in transatlantischen Verhältnissen Rahmenbedingungen entwickeln könnten, die dann sowohl in den USA als auch in Europa gelten können.
-Und wir müssten dann bei den Produkten eben auch keine unterschiedlichen Umsetzungen machen.
-Und das würde natürlich das Ganze auch erleichtern.
-Hahne: Ich höre hier allerdings auch viel den Konjunktiv.
-Das heißt, noch ist die Politik da nicht Ihren Wünschen gemäß dem nachgekommen?
-Mattes: Nein, wir sind eben noch nicht an einem Punkt, wo wir sagen können, da liegt was vor, über das wir uns jetzt austauschen können.
-Aber natürlich ist die Politik involviert und kümmert sich auch da drum gemeinsam mit uns.
-Es gibt ja auch die Testfelder schon, es gibt die Regionen, wo autonom erprobt werden darf.
-Und wir müssen jetzt aus diesen ganzen Erprobungen heraus dann auch die richtigen Rahmenbedingungen setzen, das ist klar.
-Hahne: Sie haben es angesprochen, 2021 will Ford Fahrdiensten wie Uber zum Beispiel selbstfahrende Autos anbieten.
-Wann, glauben Sie, werden denn Otto–Normal-Kunden das erste selbstfahrende Ford-Auto kaufen können?
-Mattes: 2021.
-Denn dann werden wir diese Fahrzeuge tatsächlich auf den Markt bringen.
-Ich bin aber überzeugt, dass die größte Nachfrage nicht bei denjenigen sein wird, die die Fahrzeuge direkt kaufen, sondern vielmehr, die solche Fahrzeuge nutzen, die halt von A nach B in die Welt gebracht werden wollen, aber nicht unbedingt sagen, das Auto muss mir gehören.
-Hahne: Zu Gast im Deutschlandfunk Interview der Woche ist Bernhard Mattes, Vorsitzender der Geschäftsführung von Ford Deutschland.
-Herr Mattes, nicht nur das Auto wird sich in Zukunft verändern, sondern auch wie es gebaut wird, Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Industrie 4.0"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" , also die Vernetzung der gesamten Wertschöpfungskette.
-Vor rund 100 Jahren hat Ford eines der ersten permanenten Fließbänder in der Produktion eingeführt.
-Betrachten Sie sich auch in Sachen Industrie 4.0 als Vorreiter, sozusagen aus der historischen Tradition heraus?
-Mattes: Die Weiterentwicklung der Effizienz unserer Produktion ist schon immer eine hohe Priorität bei uns gewesen, sehr effizient Produkte zu fertigen ist auch eine Notwendigkeit insbesondere, wenn sie im Volumensegment sind, da haben die Kosten natürlich einen hohen Stellenwert, beziehungsweise die Kosten möglichst gering zu halten.
-Und wir haben mit Industrie 4.0 schon sehr, sehr früh angefangen und heute haben wir Industrie 4.0 in vielen, vielen Bereichen komplett umgesetzt.
-Das heißt, wir sind nicht nur, was die Fertigung angeht, in der Planung vollkommen virtuell erstmal unterwegs.
-Wir planen die einzelnen Stationen virtuell, wir wissen, welche Gewichte dort verarbeitet werden müssen, wie das alles abläuft, das wird alles virtuell dargestellt, um dann die Arbeitsabläufe so optimal wie möglich zu gestalten.
-Die Vernetzung mit den manuell tätigen Mitarbeiterinnen und Mitarbeitern und Computern und Robotern haben wir ebenfalls schon hier in die Tat umgesetzt.
-Und letztlich kommunizieren auch schon Teile bei der Produktion miteinander.
-Wenn Sie sich unsere Motorenfertigung anschauen, da wissen die einzelnen Bauteile, welches von seiner Ausprägung, von seiner Größe in ganz genauer Messgenauigkeit, in hoher Messgenauigkeit zum anderen am besten passt.
-Und so werden die Motoren dann auch zusammengebaut.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es kommen natürlich andere Voraussetzungen auf die Mitarbeiter zu"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Hahne: Und was heißt das für die Mitarbeiter von heute?
-Mattes: Nun, es kommen natürlich andere Voraussetzungen auf die Mitarbeiter zu.
-Neben der manuellen Tätigkeit ist die Bedienung von Computern, von Maschinen, von Robotern heute eine Aufgabe, die fast gang und gäbe geworden ist.
-Das ist auf der einen Seite etwas Neues, auf der anderen Seite natürlich auch für die Mitarbeiterinnen und Mitarbeiter spannend, etwas Neues hinzulernen zu können.
-Und letztlich macht es aber auch die Arbeit leichter, weil wir, wenn Sie sich unsere Produktion anschauen, viele, viele früher beschwerliche Arbeitsgänge heute über Computerisierung, über Roboter und Ähnliches ganz anders gestaltet haben, und die körperliche Beanspruchung der Mitarbeiterinnen und Mitarbeiter ist deutlich geringer.
-Hahne: Im Business Barometer der deutsch-amerikanischen Handelskammer kam heraus, dass etwa ein Viertel der amerikanischen Unternehmen in Deutschland mit mehr Arbeitsplätzen rechnen durch Industrie 4.0, etwa genauso viel allerdings auch mit weniger.
-Was glauben Sie denn?
-Mattes: Also, wir sehen es ja bei uns: Trotz der Umsetzung von Industrie 4.0 an unseren Standorten ist die Anzahl der Belegschaft nicht zurückgegangen.
-Es hat sich aber ein Wandel in den Arbeitsplätzen ergeben, wie ich vorhin schon ausführte.
-Die sind anspruchsvoller geworden, da sind neue Themen hinzugekommen, die auch neu gelernt werden mussten.
-Wir haben ein hohes Maß an Training aufgewandt in den letzten Jahren, wenn es zu neuen Produkten und neuen Produktionsformen kam.
-Also, wir sehen keinen Schwund an Arbeitsplätzen, aber eine andere Qualität an Arbeitsplätzen.
-Hahne: Wenn wir von den Fachkräften der Zukunft sprechen - als im letzten Jahr viele Flüchtlinge nach Deutschland gekommen sind, war die Wirtschaft zunächst relativ euphorisch.
-Die Hoffnung, die mitschwang, war: die Zuwanderung könnte unser demografisches Problem lösen.
-Mittlerweise ist klar, automatisch wird das nicht passieren.
-Ford hat ein Praktikantenprogramm für Flüchtlinge – welche Erfahrungen haben Sie gesammelt?
-Mattes: Also, wir hatten schon die ersten Flüchtlinge in diesem Programm.
-Wir haben positive Erfahrungen gesammelt in mehrerlei Hinsicht.
-Erstens einmal, das waren hochmotivierte oder sind hochmotivierte Menschen, die sich in ein solches Programm begeben, weil sie wissen, was auf sie zukommt.
-Sie werden lernen müssen, sie werden körperlich arbeiten müssen und die deutsche Sprache erlernen, also dreierlei Voraussetzungen.
-Das ist sehr positiv angelaufen.
-Wir werden jetzt eine nächste Gruppe von 24 Flüchtlingen in dieses Qualifizierungsprogramm bringen, wo sie eben soweit fit gemacht werden, dass sie dann im Arbeitsmarkt in eine reguläre Ausbildung einsteigen können.
-Und das hat sich bewährt und wir sind froh, dass wir eben diese Plätze auch bereitstellen können.
-Denn wichtig ist, dass die Menschen, die es wollen, tatsächlich auch die Voraussetzungen schaffen, um dann im Arbeitsmarkt erfolgreich sein zu können.
-Hahne: Arbeiten die eigentlich nur in der Produktion oder auch in der Verwaltung?
-Mattes: Nein, die sind in der Produktion, und da können wir auch genau sehr schön im Prinzip abbilden, was die Leute können und was die Leute wollen, und das passt hervorragend zusammen.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Protektionismus ist in einer immer vernetzteren Welt genau das Falsche"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Hahne: Sie sind nicht nur als Manager in einem deutsch-amerikanischen Konzern ein USA-Kenner, Sie waren schon als Jugendlicher das erste Mal in den USA bei einer Gastfamilie.
-Aktuell läuft ja dort der Präsidentschaftswahlkampf auf Hochtouren.
-Beide Kandidaten schlagen protektionistische Töne an.
-Sorgt Sie das einerseits als USA-Liebhaber, andererseits aber auch als Manager?
-Die USA sind ja immerhin auch der wichtigste Exportmarkt für Deutschland.
-Mattes: Grundsätzlich, ungeachtet jetzt des Präsidentschaftswahlkampfs, ist Protektionismus in einer immer vernetzteren Welt genau das Falsche.
-Freier und fairer Handel, offene Grenzen – aber wie ich sagte, fair auch was Währungsgestaltung angeht –, das ist etwas, was wir befürworten, was ich befürworte, was Ford befürwortet und was auch sicherlich für die USA schon immer etwas war.
-Die USA war immer offen, offen in der Entwicklung neuer Ideen und diese dann auch in die Welt hinauszutragen und nicht nur für sich selber zu sorgen.
-Von daher gesehen bin ich überzeugt, dass es das richtige Mittel ist, weiterhin freien und fairen Handel und wenig Protektionismus zu fordern und zu fördern.
-Wir werden sehen, welcher der Kandidaten letztlich Präsidentin oder Präsident wird.
-Und ich bin überzeugt, dass der Grundsatz von freiem und fairen Handel auch den nächsten Präsidenten oder die nächste Präsidentin schnell überzeugen wird.
-Hahne: Haben Sie da bei Clinton oder Trump größere Hoffnung, bei dem ein oder anderen Kandidaten?
-Mattes: Ich sehe zumindest in den Ankündigungen, dass Frau Clinton eher für einen offenen Handel ist, sicherlich sehr dezidiert und unterschiedlich, was die derzeit diskutierten Freihandelsabkommen angeht – das transpazifische eher kritisch, das europäisch-amerikanische, glaube ich, eher offen.
-Natürlich weist sie auf einige Punkte hin, wie Arbeitnehmerrecht und Ähnliches, aber das ist klar.
-Das ist in den Verhandlungen jetzt auch noch zu Ende zu verhandeln, aber vom Grundsatz her, glaube ich, ist da eine Offenheit da.
-Starke Wettbewerbsposition für mehr Innovation und sichere Arbeitsplätze Hahne: Hillary Clinton wäre Ihnen also die liebere US-Präsidentin?
-Mattes: Das will ich jetzt damit nicht gesagt haben.
-Ich glaube auch, dass ein anderer Präsident, nämlich Donald Trump als Wirtschafskenner, sehr schnell erkennt, dass Protektionismus keine Dauerlösung ist, sondern letztlich Weltoffenheit, wenn es darum geht, Innovationen, Investitionen und auch Handel zu fördern, das richtige Mittel ist.
-Hahne: Es klang ja schon an, Sie sind auch Befürworter des Freihandelsabkommens TTIP. Mittlerweile ist ja nicht mehr so sicher, ob das bis November abschließend verhandelt wird und ob es danach eine Chance hat, das wird dann eben die Zukunft zeigen.
-Würden Sie im Zweifelsfall – anders als früher – jetzt auch für einen Teilbeschluss von einzelnen Paketen plädieren?
-Mattes: Das hat zwei Aspekte.
-Auf der einen Seite, wenn man sich heute dazu durchringt zu sagen: Okay, wir machen einen Teilabschluss – dann hat man vielleicht einen Teilsieg errungen, indem wir einen Teil von Reglungen tatsächlich dann harmonisieren und offen gestalten, aber das Andere ist dann eben nicht geregelt.
-Und deswegen bin ich nach wie vor dafür, keine Ausschlüsse zu machen und ein so umfassend wie mögliches Abkommen zu gestalten und einen Rahmenentwurf bis zum Jahresende zu setzen, der ja dann erstmal in die parlamentarische Beratung auch geht und sowohl in den USA als auch in den europäischen Ländern zu diskutieren ist.
-Möglichst umfassend ist wichtiger als Zeit.
-Zeit ist aber auch drängend, denn wir sind ja nicht alleine im Welthandel, Europa und Amerika.
-Und je mehr Zeit ins Land geht, desto weniger stärken wir die Wettbewerbsposition von Europa und Amerika im Welthandel und das sollten wir uns immer vor Augen führen: Eine starke Wettbewerbsposition hat zum Beispiel auch zur Folge, dass die in diesen Ländern ansässigen Industrien eine bessere Möglichkeit haben, Arbeitsplätze zu sichern, Innovationen zu fördern und letztlich auch Investitionen zu treiben, die weitere Arbeitsplätze schaffen können.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Am Anfang hätte man transparenter informieren sollen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Hahne: Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" parlamentarische Beratung"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" , wie zufrieden stellt Sie denn – als Bürger Bernhard Mattes und nicht als Ford-Chef Bernhard Mattes – der Ablauf der Verhandlungen, der ja insbesondere am Anfang doch recht intransparent war?
-Mattes: Ja, ich habe das persönlich auch genauso gesehen, wie Sie es eben fragen.
-Am Anfang hätte man transparenter informieren sollen.
-Das Mandat, das der EU-Kommission gegeben wurde, ist sehr klar, es wurde von allen 27 Mitgliedsstaaten ratifiziert.
-Das hätte man ohne Weiteres zu Beginn der Verhandlungen und nicht erst zwei Jahre später veröffentlichen können.
-Denn darin können heute alle Bürger lesen – jetzt ist es ja schon lange transparent und im Internet verfügbar –, was sind denn eigentlich die Grundlinien und Richtwerte und Felder der Verhandlungen.
-Da ist alles sehr transparent beschrieben.
-Da ist auch klar beschrieben, in welche Richtung zu verhandeln ist, was das Mandat ist und was es nicht ist.
-Das hätte man früher machen sollen.
-Hahne: Und jetzt nochmal Frage an den Manager: Besonders kritisch diskutiert werden ja die Schiedsgerichte nach wie vor – die politischen Systeme in den USA und Europa bieten Unternehmen ja ziemlich viel Rechtssicherheit.
-Halten Sie Schiedsgerichte trotzdem für ein geeignetes Instrument zum Investorenschutz?
-Mattes: Auf jeden Fall.
-Und ich halte das auch innerhalb von TTIP für das richtige Instrument.
-Weil TTIP kann auch eine Art Blaupause für weitere Freihandelsabkommen sein oder auch ein Abkommen eines Wirtschaftsraumes, der sich weiter öffnen kann, auch weitere Mitglieder noch aufnehmen kann.
-Und um genau diese Möglichkeit aufrecht zu erhalten, sollte man über den Investorenschutz und die Schiedsgerichte auch hier eine Klausel finden.
-Wir haben es ja auch in CETA, in dem Abkommen zwischen der EU und Kanada drin – auch zwei Systeme, die absolut von der Rechtssicherheit in Ordnung sind.
-Es gibt natürlich schon ein Gefälle auch innerhalb der EU, das darf man nicht verkennen.
-Trotzdem, die Bundesrepublik Deutschland hat in 130 Fällen in Freihandelsabkommen Schiedsgerichtsklauseln und Investorenschutzabkommen verankert.
-Um einfach eines sicherzustellen, dass Firmen sowohl im Inland als auch im Ausland, wenn es um willkürliche Veränderungen und Diskriminierung geht, hier vorgehen können.
-Es gilt auch für kleinere Unternehmen, kleinere und mittlere, die mittlerweile ja auch global unterwegs sind, die im Zweifelsfall gar nicht die Möglichkeit haben, weil sie gar nicht die Rechtsabteilungen in ihren Unternehmen haben, ihre Rechte einzufordern.
-Es geht nicht darum, dass man gegen bestehendes Gesetz und Recht klagen kann, dafür ist die normale Gerichtsbarkeit zuständig.
-Das ist auch ein wichtiger Unterschied, der zu machen ist.
-Hahne: Herr Mattes, vielen Dank für das Gespräch.
-Mattes: Bitteschön.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -630,6 +526,104 @@
 Ich glaube, wir müssen unsere Ausgaben für Forschung und Entwicklung erhöhen.
 Wir werden dafür sorgen müssen, dass junge Unternehmen mehr Chancen haben.
 Wir müssen dafür sorgen, dass die berufliche Bildung wieder an Stellenwert gewinnt – wir haben einen Fachkräftemangel bei uns.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hahne: Zu Gast im Deutschlandfunk Interview der Woche ist Bernhard Mattes, Vorsitzender der Geschäftsführung von Ford Deutschland.
+Herr Mattes, nicht nur das Auto wird sich in Zukunft verändern, sondern auch wie es gebaut wird, Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Industrie 4.0"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" , also die Vernetzung der gesamten Wertschöpfungskette.
+Vor rund 100 Jahren hat Ford eines der ersten permanenten Fließbänder in der Produktion eingeführt.
+Betrachten Sie sich auch in Sachen Industrie 4.0 als Vorreiter, sozusagen aus der historischen Tradition heraus?
+Mattes: Die Weiterentwicklung der Effizienz unserer Produktion ist schon immer eine hohe Priorität bei uns gewesen, sehr effizient Produkte zu fertigen ist auch eine Notwendigkeit insbesondere, wenn sie im Volumensegment sind, da haben die Kosten natürlich einen hohen Stellenwert, beziehungsweise die Kosten möglichst gering zu halten.
+Und wir haben mit Industrie 4.0 schon sehr, sehr früh angefangen und heute haben wir Industrie 4.0 in vielen, vielen Bereichen komplett umgesetzt.
+Das heißt, wir sind nicht nur, was die Fertigung angeht, in der Planung vollkommen virtuell erstmal unterwegs.
+Wir planen die einzelnen Stationen virtuell, wir wissen, welche Gewichte dort verarbeitet werden müssen, wie das alles abläuft, das wird alles virtuell dargestellt, um dann die Arbeitsabläufe so optimal wie möglich zu gestalten.
+Die Vernetzung mit den manuell tätigen Mitarbeiterinnen und Mitarbeitern und Computern und Robotern haben wir ebenfalls schon hier in die Tat umgesetzt.
+Und letztlich kommunizieren auch schon Teile bei der Produktion miteinander.
+Wenn Sie sich unsere Motorenfertigung anschauen, da wissen die einzelnen Bauteile, welches von seiner Ausprägung, von seiner Größe in ganz genauer Messgenauigkeit, in hoher Messgenauigkeit zum anderen am besten passt.
+Und so werden die Motoren dann auch zusammengebaut.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es kommen natürlich andere Voraussetzungen auf die Mitarbeiter zu"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Hahne: Und was heißt das für die Mitarbeiter von heute?
+Mattes: Nun, es kommen natürlich andere Voraussetzungen auf die Mitarbeiter zu.
+Neben der manuellen Tätigkeit ist die Bedienung von Computern, von Maschinen, von Robotern heute eine Aufgabe, die fast gang und gäbe geworden ist.
+Das ist auf der einen Seite etwas Neues, auf der anderen Seite natürlich auch für die Mitarbeiterinnen und Mitarbeiter spannend, etwas Neues hinzulernen zu können.
+Und letztlich macht es aber auch die Arbeit leichter, weil wir, wenn Sie sich unsere Produktion anschauen, viele, viele früher beschwerliche Arbeitsgänge heute über Computerisierung, über Roboter und Ähnliches ganz anders gestaltet haben, und die körperliche Beanspruchung der Mitarbeiterinnen und Mitarbeiter ist deutlich geringer.
+Hahne: Im Business Barometer der deutsch-amerikanischen Handelskammer kam heraus, dass etwa ein Viertel der amerikanischen Unternehmen in Deutschland mit mehr Arbeitsplätzen rechnen durch Industrie 4.0, etwa genauso viel allerdings auch mit weniger.
+Was glauben Sie denn?
+Mattes: Also, wir sehen es ja bei uns: Trotz der Umsetzung von Industrie 4.0 an unseren Standorten ist die Anzahl der Belegschaft nicht zurückgegangen.
+Es hat sich aber ein Wandel in den Arbeitsplätzen ergeben, wie ich vorhin schon ausführte.
+Die sind anspruchsvoller geworden, da sind neue Themen hinzugekommen, die auch neu gelernt werden mussten.
+Wir haben ein hohes Maß an Training aufgewandt in den letzten Jahren, wenn es zu neuen Produkten und neuen Produktionsformen kam.
+Also, wir sehen keinen Schwund an Arbeitsplätzen, aber eine andere Qualität an Arbeitsplätzen.
+Hahne: Wenn wir von den Fachkräften der Zukunft sprechen - als im letzten Jahr viele Flüchtlinge nach Deutschland gekommen sind, war die Wirtschaft zunächst relativ euphorisch.
+Die Hoffnung, die mitschwang, war: die Zuwanderung könnte unser demografisches Problem lösen.
+Mittlerweise ist klar, automatisch wird das nicht passieren.
+Ford hat ein Praktikantenprogramm für Flüchtlinge – welche Erfahrungen haben Sie gesammelt?
+Mattes: Also, wir hatten schon die ersten Flüchtlinge in diesem Programm.
+Wir haben positive Erfahrungen gesammelt in mehrerlei Hinsicht.
+Erstens einmal, das waren hochmotivierte oder sind hochmotivierte Menschen, die sich in ein solches Programm begeben, weil sie wissen, was auf sie zukommt.
+Sie werden lernen müssen, sie werden körperlich arbeiten müssen und die deutsche Sprache erlernen, also dreierlei Voraussetzungen.
+Das ist sehr positiv angelaufen.
+Wir werden jetzt eine nächste Gruppe von 24 Flüchtlingen in dieses Qualifizierungsprogramm bringen, wo sie eben soweit fit gemacht werden, dass sie dann im Arbeitsmarkt in eine reguläre Ausbildung einsteigen können.
+Und das hat sich bewährt und wir sind froh, dass wir eben diese Plätze auch bereitstellen können.
+Denn wichtig ist, dass die Menschen, die es wollen, tatsächlich auch die Voraussetzungen schaffen, um dann im Arbeitsmarkt erfolgreich sein zu können.
+Hahne: Arbeiten die eigentlich nur in der Produktion oder auch in der Verwaltung?
+Mattes: Nein, die sind in der Produktion, und da können wir auch genau sehr schön im Prinzip abbilden, was die Leute können und was die Leute wollen, und das passt hervorragend zusammen.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Protektionismus ist in einer immer vernetzteren Welt genau das Falsche"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Hahne: Sie sind nicht nur als Manager in einem deutsch-amerikanischen Konzern ein USA-Kenner, Sie waren schon als Jugendlicher das erste Mal in den USA bei einer Gastfamilie.
+Aktuell läuft ja dort der Präsidentschaftswahlkampf auf Hochtouren.
+Beide Kandidaten schlagen protektionistische Töne an.
+Sorgt Sie das einerseits als USA-Liebhaber, andererseits aber auch als Manager?
+Die USA sind ja immerhin auch der wichtigste Exportmarkt für Deutschland.
+Mattes: Grundsätzlich, ungeachtet jetzt des Präsidentschaftswahlkampfs, ist Protektionismus in einer immer vernetzteren Welt genau das Falsche.
+Freier und fairer Handel, offene Grenzen – aber wie ich sagte, fair auch was Währungsgestaltung angeht –, das ist etwas, was wir befürworten, was ich befürworte, was Ford befürwortet und was auch sicherlich für die USA schon immer etwas war.
+Die USA war immer offen, offen in der Entwicklung neuer Ideen und diese dann auch in die Welt hinauszutragen und nicht nur für sich selber zu sorgen.
+Von daher gesehen bin ich überzeugt, dass es das richtige Mittel ist, weiterhin freien und fairen Handel und wenig Protektionismus zu fordern und zu fördern.
+Wir werden sehen, welcher der Kandidaten letztlich Präsidentin oder Präsident wird.
+Und ich bin überzeugt, dass der Grundsatz von freiem und fairen Handel auch den nächsten Präsidenten oder die nächste Präsidentin schnell überzeugen wird.
+Hahne: Haben Sie da bei Clinton oder Trump größere Hoffnung, bei dem ein oder anderen Kandidaten?
+Mattes: Ich sehe zumindest in den Ankündigungen, dass Frau Clinton eher für einen offenen Handel ist, sicherlich sehr dezidiert und unterschiedlich, was die derzeit diskutierten Freihandelsabkommen angeht – das transpazifische eher kritisch, das europäisch-amerikanische, glaube ich, eher offen.
+Natürlich weist sie auf einige Punkte hin, wie Arbeitnehmerrecht und Ähnliches, aber das ist klar.
+Das ist in den Verhandlungen jetzt auch noch zu Ende zu verhandeln, aber vom Grundsatz her, glaube ich, ist da eine Offenheit da.
+Starke Wettbewerbsposition für mehr Innovation und sichere Arbeitsplätze Hahne: Hillary Clinton wäre Ihnen also die liebere US-Präsidentin?
+Mattes: Das will ich jetzt damit nicht gesagt haben.
+Ich glaube auch, dass ein anderer Präsident, nämlich Donald Trump als Wirtschafskenner, sehr schnell erkennt, dass Protektionismus keine Dauerlösung ist, sondern letztlich Weltoffenheit, wenn es darum geht, Innovationen, Investitionen und auch Handel zu fördern, das richtige Mittel ist.
+Hahne: Es klang ja schon an, Sie sind auch Befürworter des Freihandelsabkommens TTIP. Mittlerweile ist ja nicht mehr so sicher, ob das bis November abschließend verhandelt wird und ob es danach eine Chance hat, das wird dann eben die Zukunft zeigen.
+Würden Sie im Zweifelsfall – anders als früher – jetzt auch für einen Teilbeschluss von einzelnen Paketen plädieren?
+Mattes: Das hat zwei Aspekte.
+Auf der einen Seite, wenn man sich heute dazu durchringt zu sagen: Okay, wir machen einen Teilabschluss – dann hat man vielleicht einen Teilsieg errungen, indem wir einen Teil von Reglungen tatsächlich dann harmonisieren und offen gestalten, aber das Andere ist dann eben nicht geregelt.
+Und deswegen bin ich nach wie vor dafür, keine Ausschlüsse zu machen und ein so umfassend wie mögliches Abkommen zu gestalten und einen Rahmenentwurf bis zum Jahresende zu setzen, der ja dann erstmal in die parlamentarische Beratung auch geht und sowohl in den USA als auch in den europäischen Ländern zu diskutieren ist.
+Möglichst umfassend ist wichtiger als Zeit.
+Zeit ist aber auch drängend, denn wir sind ja nicht alleine im Welthandel, Europa und Amerika.
+Und je mehr Zeit ins Land geht, desto weniger stärken wir die Wettbewerbsposition von Europa und Amerika im Welthandel und das sollten wir uns immer vor Augen führen: Eine starke Wettbewerbsposition hat zum Beispiel auch zur Folge, dass die in diesen Ländern ansässigen Industrien eine bessere Möglichkeit haben, Arbeitsplätze zu sichern, Innovationen zu fördern und letztlich auch Investitionen zu treiben, die weitere Arbeitsplätze schaffen können.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Am Anfang hätte man transparenter informieren sollen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Hahne: Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" parlamentarische Beratung"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" , wie zufrieden stellt Sie denn – als Bürger Bernhard Mattes und nicht als Ford-Chef Bernhard Mattes – der Ablauf der Verhandlungen, der ja insbesondere am Anfang doch recht intransparent war?
+Mattes: Ja, ich habe das persönlich auch genauso gesehen, wie Sie es eben fragen.
+Am Anfang hätte man transparenter informieren sollen.
+Das Mandat, das der EU-Kommission gegeben wurde, ist sehr klar, es wurde von allen 27 Mitgliedsstaaten ratifiziert.
+Das hätte man ohne Weiteres zu Beginn der Verhandlungen und nicht erst zwei Jahre später veröffentlichen können.
+Denn darin können heute alle Bürger lesen – jetzt ist es ja schon lange transparent und im Internet verfügbar –, was sind denn eigentlich die Grundlinien und Richtwerte und Felder der Verhandlungen.
+Da ist alles sehr transparent beschrieben.
+Da ist auch klar beschrieben, in welche Richtung zu verhandeln ist, was das Mandat ist und was es nicht ist.
+Das hätte man früher machen sollen.
+Hahne: Und jetzt nochmal Frage an den Manager: Besonders kritisch diskutiert werden ja die Schiedsgerichte nach wie vor – die politischen Systeme in den USA und Europa bieten Unternehmen ja ziemlich viel Rechtssicherheit.
+Halten Sie Schiedsgerichte trotzdem für ein geeignetes Instrument zum Investorenschutz?
+Mattes: Auf jeden Fall.
+Und ich halte das auch innerhalb von TTIP für das richtige Instrument.
+Weil TTIP kann auch eine Art Blaupause für weitere Freihandelsabkommen sein oder auch ein Abkommen eines Wirtschaftsraumes, der sich weiter öffnen kann, auch weitere Mitglieder noch aufnehmen kann.
+Und um genau diese Möglichkeit aufrecht zu erhalten, sollte man über den Investorenschutz und die Schiedsgerichte auch hier eine Klausel finden.
+Wir haben es ja auch in CETA, in dem Abkommen zwischen der EU und Kanada drin – auch zwei Systeme, die absolut von der Rechtssicherheit in Ordnung sind.
+Es gibt natürlich schon ein Gefälle auch innerhalb der EU, das darf man nicht verkennen.
+Trotzdem, die Bundesrepublik Deutschland hat in 130 Fällen in Freihandelsabkommen Schiedsgerichtsklauseln und Investorenschutzabkommen verankert.
+Um einfach eines sicherzustellen, dass Firmen sowohl im Inland als auch im Ausland, wenn es um willkürliche Veränderungen und Diskriminierung geht, hier vorgehen können.
+Es gilt auch für kleinere Unternehmen, kleinere und mittlere, die mittlerweile ja auch global unterwegs sind, die im Zweifelsfall gar nicht die Möglichkeit haben, weil sie gar nicht die Rechtsabteilungen in ihren Unternehmen haben, ihre Rechte einzufordern.
+Es geht nicht darum, dass man gegen bestehendes Gesetz und Recht klagen kann, dafür ist die normale Gerichtsbarkeit zuständig.
+Das ist auch ein wichtiger Unterschied, der zu machen ist.
+Hahne: Herr Mattes, vielen Dank für das Gespräch.
+Mattes: Bitteschön.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Es ist auch ein klassisches Feld
+Hahne: Ich höre hier allerdings auch viel den Konjunktiv.
+Das heißt, noch ist die Politik da nicht Ihren Wünschen gemäß.
+Aber natürlich ist die Politik involviert und , die halt von A nach B in die Welt gebracht werden wollen, aber nicht unbedingt sagen, das Auto muss mir gehören.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -966,7 +960,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +979,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="378" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -995,6 +989,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B1EF6A-EC66-4EEA-B893-28B1745B3493}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.08203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="154" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -1028,16 +1041,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
